--- a/docs/downloads/13/tbl_repondant_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/13/tbl_repondant_alaotra_feramanga_atsimo.xlsx
@@ -442,9 +442,6 @@
           <t>Code NA</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
